--- a/output.xlsx
+++ b/output.xlsx
@@ -46,11 +46,11 @@
       <color rgb="009C0006"/>
     </font>
     <font>
-      <color rgb="00AAAAAA"/>
+      <color rgb="00BBBBBB"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00595959"/>
+      <color rgb="00AAAAAA"/>
     </font>
     <font>
       <b val="1"/>
@@ -60,7 +60,7 @@
       <color rgb="00595959"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -69,7 +69,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="00EF7B88"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,12 +94,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFCCB3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -172,7 +177,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>

--- a/output.xlsx
+++ b/output.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michalkassa/Desktop/lp-outreach/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3480E478-5B8E-B245-86E8-18E40A3D2BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09DB5B0D-C55A-934E-B546-40E303401B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="311">
   <si>
     <t>Country</t>
   </si>
@@ -212,9 +212,6 @@
     <t>vbv-vorsorgekasse-ag</t>
   </si>
   <si>
-    <t>&gt;€1.5B</t>
-  </si>
-  <si>
     <t>Confirmed private debt and stable real estate allocation despite capital guarantee structure</t>
   </si>
   <si>
@@ -293,9 +290,6 @@
     <t>nestle-pensionsfonds-ag</t>
   </si>
   <si>
-    <t>no contact</t>
-  </si>
-  <si>
     <t>integrated into German entity 2015 — do not contact</t>
   </si>
   <si>
@@ -945,13 +939,31 @@
   </si>
   <si>
     <t>Regulatory barrier or AUM too small</t>
+  </si>
+  <si>
+    <t>Christian Jacob</t>
+  </si>
+  <si>
+    <t>Chairman</t>
+  </si>
+  <si>
+    <t>NestleRente@neversa.de</t>
+  </si>
+  <si>
+    <t>€382.406M</t>
+  </si>
+  <si>
+    <t>€3.1717B</t>
+  </si>
+  <si>
+    <t>17.8B</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -964,41 +976,56 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF375623"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF833C00"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1068,10 +1095,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1079,26 +1107,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1106,17 +1122,21 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1492,7 +1512,7 @@
       <c r="D2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="15">
         <v>92</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -1507,13 +1527,13 @@
       <c r="I2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>24</v>
       </c>
       <c r="M2" s="2"/>
@@ -1532,7 +1552,7 @@
       <c r="D3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="15">
         <v>68</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -1553,7 +1573,7 @@
       <c r="K3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="4" t="s">
         <v>32</v>
       </c>
       <c r="M3" s="2"/>
@@ -1572,7 +1592,7 @@
       <c r="D4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="15">
         <v>82</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -1593,7 +1613,7 @@
       <c r="K4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="4" t="s">
         <v>39</v>
       </c>
       <c r="M4" s="2"/>
@@ -1612,7 +1632,7 @@
       <c r="D5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="15">
         <v>88</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -1633,7 +1653,7 @@
       <c r="K5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="4" t="s">
         <v>46</v>
       </c>
       <c r="M5" s="2"/>
@@ -1652,7 +1672,7 @@
       <c r="D6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="15">
         <v>78</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -1673,7 +1693,7 @@
       <c r="K6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="L6" s="4" t="s">
         <v>53</v>
       </c>
       <c r="M6" s="2"/>
@@ -1692,28 +1712,20 @@
       <c r="D7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="15">
         <v>25</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>56</v>
-      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="14"/>
       <c r="J7" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L7" s="5" t="s">
+      <c r="L7" s="4" t="s">
         <v>57</v>
       </c>
       <c r="M7" s="2" t="s">
@@ -1734,11 +1746,11 @@
       <c r="D8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="15">
         <v>58</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>62</v>
+        <v>310</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>19</v>
@@ -1755,53 +1767,53 @@
       <c r="K8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="L8" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="N8" s="2"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="8" t="s">
+      <c r="C9" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="E9" s="15">
+        <v>5</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="9">
-        <v>5</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="G9" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="H9" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="I9" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="J9" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="K9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="7"/>
+      <c r="M9" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="K9" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="11"/>
-      <c r="M9" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="N9" s="8"/>
+      <c r="N9" s="5"/>
     </row>
     <row r="10" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
@@ -1811,25 +1823,25 @@
         <v>15</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="15">
+        <v>48</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E10" s="12">
-        <v>48</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>31</v>
@@ -1837,8 +1849,8 @@
       <c r="K10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L10" s="5" t="s">
-        <v>79</v>
+      <c r="L10" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -1851,25 +1863,25 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="15">
+        <v>22</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E11" s="7">
-        <v>22</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>31</v>
@@ -1877,82 +1889,88 @@
       <c r="K11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L11" s="5"/>
+      <c r="L11" s="4"/>
       <c r="M11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="N11" s="2"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="N11" s="2"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="E12" s="15">
+        <v>5</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" s="7"/>
+      <c r="M12" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E12" s="9">
-        <v>5</v>
-      </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="L12" s="11"/>
-      <c r="M12" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="N12" s="8"/>
+      <c r="N12" s="5"/>
     </row>
     <row r="13" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="E13" s="15">
+        <v>50</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E13" s="12">
-        <v>50</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="J13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="L13" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -1965,25 +1983,25 @@
         <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14" s="15">
+        <v>45</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E14" s="12">
-        <v>45</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="H14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>31</v>
@@ -1991,8 +2009,8 @@
       <c r="K14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L14" s="5" t="s">
-        <v>104</v>
+      <c r="L14" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2002,37 +2020,37 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15" s="15">
+        <v>80</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="E15" s="3">
-        <v>80</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>110</v>
+        <v>95</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -2042,37 +2060,37 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" s="15">
+        <v>68</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="E16" s="6">
-        <v>68</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>116</v>
+        <v>95</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -2082,40 +2100,40 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" s="15">
+        <v>48</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="E17" s="12">
-        <v>48</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I17" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="M17" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="N17" s="2"/>
     </row>
@@ -2124,37 +2142,37 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E18" s="12">
+        <v>123</v>
+      </c>
+      <c r="E18" s="15">
         <v>45</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>56</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>128</v>
+        <v>95</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>126</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -2164,37 +2182,37 @@
         <v>14</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" s="15">
+        <v>80</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="E19" s="3">
-        <v>80</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>134</v>
+        <v>95</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
@@ -2204,37 +2222,37 @@
         <v>14</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E20" s="12">
+        <v>134</v>
+      </c>
+      <c r="E20" s="15">
         <v>35</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>56</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>139</v>
+        <v>95</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -2244,40 +2262,40 @@
         <v>14</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E21" s="15">
+        <v>32</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="E21" s="7">
-        <v>32</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="M21" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L21" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="N21" s="2"/>
     </row>
@@ -2286,37 +2304,37 @@
         <v>14</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E22" s="15">
+        <v>55</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="E22" s="6">
-        <v>55</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>152</v>
+        <v>95</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>150</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -2326,37 +2344,37 @@
         <v>14</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E23" s="15">
+        <v>62</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="E23" s="6">
-        <v>62</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>158</v>
+        <v>95</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>156</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -2366,99 +2384,99 @@
         <v>14</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E24" s="12">
+        <v>158</v>
+      </c>
+      <c r="E24" s="15">
         <v>35</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>56</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L24" s="5" t="s">
-        <v>163</v>
+        <v>95</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
     </row>
     <row r="25" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="E25" s="15">
+        <v>40</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="E25" s="12">
-        <v>40</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>170</v>
+        <v>95</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>168</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
     </row>
     <row r="26" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E26" s="15">
+        <v>28</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E26" s="7">
-        <v>28</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>56</v>
@@ -2467,411 +2485,411 @@
         <v>29</v>
       </c>
       <c r="I26" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="M26" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="N26" s="2"/>
     </row>
     <row r="27" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E27" s="15">
+        <v>28</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="E27" s="7">
-        <v>28</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I27" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="M27" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L27" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="N27" s="2"/>
     </row>
     <row r="28" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E28" s="7">
+        <v>183</v>
+      </c>
+      <c r="E28" s="15">
         <v>30</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>56</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>187</v>
+      <c r="I28" s="14" t="s">
+        <v>185</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>188</v>
+        <v>95</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>186</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
     </row>
     <row r="29" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E29" s="12">
+        <v>188</v>
+      </c>
+      <c r="E29" s="15">
         <v>40</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>56</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L29" s="5" t="s">
-        <v>193</v>
+        <v>95</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>191</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
     </row>
     <row r="30" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E30" s="12">
+        <v>193</v>
+      </c>
+      <c r="E30" s="15">
         <v>45</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>56</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>198</v>
+        <v>95</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
     </row>
     <row r="31" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E31" s="7">
+        <v>198</v>
+      </c>
+      <c r="E31" s="15">
         <v>30</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>56</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L31" s="5" t="s">
-        <v>203</v>
+        <v>95</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>201</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
     </row>
     <row r="32" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E32" s="12">
+        <v>203</v>
+      </c>
+      <c r="E32" s="15">
         <v>38</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>56</v>
       </c>
       <c r="G32" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="I32" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="J32" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L32" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L32" s="5" t="s">
-        <v>209</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
     </row>
     <row r="33" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E33" s="15">
+        <v>25</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="G33" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="E33" s="7">
-        <v>25</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L33" s="5" t="s">
-        <v>215</v>
+        <v>95</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B34" s="8" t="s">
+      <c r="A34" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="E34" s="15">
+        <v>15</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="G34" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="E34" s="9">
+      <c r="H34" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" s="7"/>
+      <c r="M34" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="N34" s="5"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E35" s="15">
         <v>15</v>
       </c>
-      <c r="F34" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="J34" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="K34" s="8" t="s">
+      <c r="F35" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K35" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="L34" s="11"/>
-      <c r="M34" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="N34" s="8"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="E35" s="9">
-        <v>15</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="H35" s="8" t="s">
+      <c r="L35" s="7"/>
+      <c r="M35" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="I35" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="L35" s="11"/>
-      <c r="M35" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="N35" s="8"/>
+      <c r="N35" s="5"/>
     </row>
     <row r="36" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="E36" s="15">
+        <v>22</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E36" s="7">
-        <v>22</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>233</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>31</v>
@@ -2879,121 +2897,121 @@
       <c r="K36" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L36" s="5" t="s">
+      <c r="L36" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="N36" s="2"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="M36" s="2" t="s">
+      <c r="D37" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="N36" s="2"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A37" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="C37" s="8" t="s">
+      <c r="E37" s="15">
+        <v>15</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" s="7"/>
+      <c r="M37" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="N37" s="5"/>
+    </row>
+    <row r="38" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D38" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="E37" s="9">
-        <v>15</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="H37" s="8" t="s">
+      <c r="E38" s="15">
+        <v>18</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="H38" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I37" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="J37" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="K37" s="8" t="s">
+      <c r="I38" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K38" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="L37" s="11"/>
-      <c r="M37" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="N37" s="8"/>
-    </row>
-    <row r="38" spans="1:14" ht="32" x14ac:dyDescent="0.2">
-      <c r="A38" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="E38" s="9">
-        <v>18</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="G38" s="8" t="s">
+      <c r="L38" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="H38" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="J38" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="K38" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="L38" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="M38" s="8"/>
-      <c r="N38" s="8"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
     </row>
     <row r="39" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E39" s="7">
+        <v>244</v>
+      </c>
+      <c r="E39" s="15">
         <v>20</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>31</v>
@@ -3001,41 +3019,41 @@
       <c r="K39" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L39" s="5" t="s">
-        <v>247</v>
+      <c r="L39" s="4" t="s">
+        <v>245</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="N39" s="2"/>
     </row>
     <row r="40" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E40" s="7">
+        <v>248</v>
+      </c>
+      <c r="E40" s="15">
         <v>22</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>31</v>
@@ -3043,81 +3061,81 @@
       <c r="K40" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L40" s="5" t="s">
+      <c r="L40" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="N40" s="2"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A41" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="M40" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="N40" s="2"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A41" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="C41" s="8" t="s">
+      <c r="E41" s="15">
+        <v>12</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="G41" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="H41" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I41" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="E41" s="9">
-        <v>12</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="G41" s="8" t="s">
+      <c r="J41" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" s="7"/>
+      <c r="M41" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="H41" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I41" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="J41" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="K41" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="L41" s="11"/>
-      <c r="M41" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="N41" s="8"/>
+      <c r="N41" s="5"/>
     </row>
     <row r="42" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="E42" s="15">
+        <v>52</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="G42" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="E42" s="12">
-        <v>52</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>262</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>31</v>
@@ -3125,39 +3143,39 @@
       <c r="K42" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L42" s="5" t="s">
-        <v>264</v>
+      <c r="L42" s="4" t="s">
+        <v>262</v>
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
     </row>
     <row r="43" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C43" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E43" s="15">
+        <v>42</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="G43" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="E43" s="12">
-        <v>42</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>268</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>31</v>
@@ -3165,39 +3183,39 @@
       <c r="K43" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L43" s="5" t="s">
-        <v>270</v>
+      <c r="L43" s="4" t="s">
+        <v>268</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
     </row>
     <row r="44" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E44" s="15">
+        <v>80</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="G44" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="E44" s="3">
-        <v>80</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>274</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>31</v>
@@ -3205,39 +3223,39 @@
       <c r="K44" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L44" s="5" t="s">
-        <v>276</v>
+      <c r="L44" s="4" t="s">
+        <v>274</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
     </row>
     <row r="45" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E45" s="15">
+        <v>50</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="G45" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="E45" s="12">
-        <v>50</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>31</v>
@@ -3245,39 +3263,39 @@
       <c r="K45" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L45" s="5" t="s">
-        <v>282</v>
+      <c r="L45" s="4" t="s">
+        <v>280</v>
       </c>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
     </row>
     <row r="46" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C46" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E46" s="15">
+        <v>72</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="G46" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="E46" s="6">
-        <v>72</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>31</v>
@@ -3285,14 +3303,18 @@
       <c r="K46" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L46" s="5" t="s">
-        <v>288</v>
+      <c r="L46" s="4" t="s">
+        <v>286</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <hyperlinks>
+    <hyperlink ref="I12" r:id="rId1" xr:uid="{5175B0FD-4849-1A41-AE4B-FCD228965C29}"/>
+    <hyperlink ref="I28" r:id="rId2" xr:uid="{265E74FE-C55A-3A48-A85D-71032C12D1BE}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -3309,69 +3331,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="B1" s="13" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="B2" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+      <c r="C2" t="s">
         <v>292</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="15" t="s">
+      <c r="C3" t="s">
         <v>295</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B4" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="16" t="s">
+      <c r="C4" t="s">
         <v>298</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
+      <c r="C5" t="s">
         <v>301</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="18" t="s">
+      <c r="C6" t="s">
         <v>304</v>
-      </c>
-      <c r="B6" t="s">
-        <v>305</v>
-      </c>
-      <c r="C6" t="s">
-        <v>306</v>
       </c>
     </row>
   </sheetData>

--- a/output.xlsx
+++ b/output.xlsx
@@ -2541,9 +2541,9 @@
           <t>nino.pavic@adriatic-osiguranje.hr</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2617,9 +2617,9 @@
           <t>jakovacm@allianz.hr</t>
         </is>
       </c>
-      <c r="L28" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -2637,7 +2637,11 @@
           <t>[CONFIRMED] — CLUSTER→allianz-pensionskasse-ag — coordinate with Allianz group rows — Matić (Allianz Österreich CEO) previously ran Allianz Croatia</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2693,9 +2697,9 @@
           <t>trendic@wiener.at</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2713,7 +2717,11 @@
           <t>[UNVERIFIED] — subsidiary of VIG — coordinate with VIG row — email domain wiener.at (group address)</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2769,9 +2777,9 @@
           <t>natasa.kapetanovic@grawe.hr</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2845,9 +2853,9 @@
           <t>mario.carini@generali.hr</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -2921,9 +2929,9 @@
           <t>tedo.djekanovic@triglav.hr</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -2997,9 +3005,9 @@
           <t>marko.klemencic@merkur.hr</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -3073,9 +3081,9 @@
           <t>kristijan.buk@azfond.hr</t>
         </is>
       </c>
-      <c r="L34" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -3149,9 +3157,9 @@
           <t>ekomunikacija@pbzco-fond.hr</t>
         </is>
       </c>
-      <c r="L35" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -3169,7 +3177,11 @@
           <t>[LIKELY] — UNGATED — entity VERIFIED: PBZ Croatia osiguranje d.d. (pbzco-fond.hr) — board: Marić (president), Goran Kralj — published contact channel — confirmed PE/VC LP interests (South Central Ventures, Prosperus)</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3225,9 +3237,9 @@
           <t>gordan.sumanovic@rmf.hr</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -3301,9 +3313,9 @@
           <t>kristijan.buk@azfond.hr</t>
         </is>
       </c>
-      <c r="L37" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -3613,9 +3625,9 @@
           <t>radojka.hainski@crosig.hr</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -3633,7 +3645,11 @@
           <t>[UNVERIFIED] — same Adris/CO group as Croatia osiguranje d.d. — fold into the group conversation</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4825,9 +4841,9 @@
           <t>d.mazarakis@ethnikiasfalistiki.gr</t>
         </is>
       </c>
-      <c r="L57" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L57" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -4845,7 +4861,11 @@
           <t>[UNVERIFIED] — verify ownership status (reported Piraeus talks) before approach</t>
         </is>
       </c>
-      <c r="P57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4901,9 +4921,9 @@
           <t>kantorosy@interamerican.gr</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L58" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -4921,7 +4941,11 @@
           <t>[UNVERIFIED] — group-framed</t>
         </is>
       </c>
-      <c r="P58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4977,9 +5001,9 @@
           <t>fekih@groupama.gr</t>
         </is>
       </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L59" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -5125,9 +5149,9 @@
           <t>panos.dimitriou@generali.gr</t>
         </is>
       </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L61" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -5145,7 +5169,11 @@
           <t>[UNVERIFIED] — shares contact with AXA Greece duplicate row — one email max</t>
         </is>
       </c>
-      <c r="P61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -5397,9 +5425,9 @@
           <t>kaskarelis@ydrogios.gr</t>
         </is>
       </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L65" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -5473,9 +5501,9 @@
           <t>ivotsaridis@interlife.gr</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L66" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -5773,9 +5801,9 @@
           <t>thompolouse@interamerican.gr</t>
         </is>
       </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L70" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -5921,9 +5949,9 @@
           <t>knebis@cosmote.gr</t>
         </is>
       </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L72" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -6069,9 +6097,9 @@
           <t>mihaly.erdos@generali.hu</t>
         </is>
       </c>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L74" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -6145,9 +6173,9 @@
           <t>bacso.gergely@allianz.hu</t>
         </is>
       </c>
-      <c r="L75" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L75" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -6165,7 +6193,11 @@
           <t>[UNVERIFIED] — CLUSTER→allianz-pensionskasse-ag — market leader — AIM framing</t>
         </is>
       </c>
-      <c r="P75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -6221,9 +6253,9 @@
           <t>alexandre.jeanjean@groupama.hu</t>
         </is>
       </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L76" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -6297,9 +6329,9 @@
           <t>havas.gabor@union.hu</t>
         </is>
       </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -6521,9 +6553,9 @@
           <t>istvan@cigpannonia.hu</t>
         </is>
       </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L80" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -6897,9 +6929,9 @@
           <t>barna.zsolt@mbhbank.hu</t>
         </is>
       </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L85" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -6973,9 +7005,9 @@
           <t>kovacs.zsolt@mpb.hu</t>
         </is>
       </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L86" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -7049,9 +7081,9 @@
           <t>wilfried-kempchen.daniel@signal.hu</t>
         </is>
       </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L87" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -7125,9 +7157,9 @@
           <t>spadlo-kolano@metlife.hu</t>
         </is>
       </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L88" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -7201,9 +7233,9 @@
           <t>tamas.marusinecz@allianz.hu</t>
         </is>
       </c>
-      <c r="L89" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L89" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -7221,7 +7253,11 @@
           <t>[UNVERIFIED] — no email in import</t>
         </is>
       </c>
-      <c r="P89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -7429,9 +7465,9 @@
           <t>tamas@mbhnyp.hu</t>
         </is>
       </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L92" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -7505,9 +7541,9 @@
           <t>marta.hanak@aranykornyp.hu</t>
         </is>
       </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L93" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -7525,7 +7561,11 @@
           <t>[UNVERIFIED] — no email in import</t>
         </is>
       </c>
-      <c r="P93" s="2" t="inlineStr"/>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -7581,9 +7621,9 @@
           <t>timea.pataki@horizontpenztar.hu</t>
         </is>
       </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L94" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -7601,7 +7641,11 @@
           <t>[UNVERIFIED] — largest surviving magannyugdijpenztar — verify AUM via MNB</t>
         </is>
       </c>
-      <c r="P94" s="2" t="inlineStr"/>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -7657,9 +7701,9 @@
           <t>poda.jeno@hnyp.hu</t>
         </is>
       </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L95" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -7733,9 +7777,9 @@
           <t>tohai.szilvia@vnyp.hu</t>
         </is>
       </c>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L96" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -7881,17 +7925,17 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>CIO</t>
+          <t>Chief Investment Officer, Unipol Gruppo and UnipolSai</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>baudir@pec.unipol.it</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+          <t>investor.relations@unipol.it</t>
+        </is>
+      </c>
+      <c r="L98" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -7906,7 +7950,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>[UNVERIFIED] — GATED(fit 56) — import email is PEC certified-mail — find standard address</t>
+          <t>[LIKELY] — Baudi confirmed as CIO (Bloomberg, MarketScreener). Published IR inbox used: the only address on file was a PEC (certified legal mail), wrong channel for outreach. No verifiable direct address. Gianluca Banfi (Head of Alternative Investments, UnipolSai) is a better desk-level target.</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr"/>
@@ -7965,9 +8009,9 @@
           <t>alberto.vacca@allianz.it</t>
         </is>
       </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L99" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -7985,7 +8029,11 @@
           <t>[UNVERIFIED] — CLUSTER→allianz-pensionskasse-ag — AIM-framed</t>
         </is>
       </c>
-      <c r="P99" s="2" t="inlineStr"/>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -8121,9 +8169,9 @@
           <t>virginia.borla@intesasanpaolo.com</t>
         </is>
       </c>
-      <c r="L101" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L101" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -8141,7 +8189,11 @@
           <t>[UNVERIFIED] — verify Borla remit</t>
         </is>
       </c>
-      <c r="P101" s="2" t="inlineStr"/>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -8197,9 +8249,9 @@
           <t>psemenzato@zurich.it</t>
         </is>
       </c>
-      <c r="L102" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L102" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -8273,9 +8325,9 @@
           <t>stephan@hdiassicurazioni.it</t>
         </is>
       </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L103" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -8349,9 +8401,9 @@
           <t>signorinimarco@helvetia.it</t>
         </is>
       </c>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L104" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -8425,9 +8477,9 @@
           <t>marco.nostini@nobisassicurazioni.it</t>
         </is>
       </c>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L105" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
@@ -8737,9 +8789,9 @@
           <t>riccardo.resciniti@fondoespero.it</t>
         </is>
       </c>
-      <c r="L109" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L109" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
@@ -8757,7 +8809,11 @@
           <t>[UNVERIFIED] — public-sector caution</t>
         </is>
       </c>
-      <c r="P109" s="2" t="inlineStr"/>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -8835,7 +8891,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -9053,9 +9109,9 @@
           <t>matteo.colamussi@fondopriamo.it</t>
         </is>
       </c>
-      <c r="L113" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L113" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
@@ -9073,7 +9129,11 @@
           <t>[UNVERIFIED] — verify FIA stance</t>
         </is>
       </c>
-      <c r="P113" s="2" t="inlineStr"/>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -9257,9 +9317,9 @@
           <t>sabina.valentini@filcoopsanitario.it</t>
         </is>
       </c>
-      <c r="L116" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L116" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
@@ -9333,9 +9393,9 @@
           <t>fabio.barigazzi@alifond.it</t>
         </is>
       </c>
-      <c r="L117" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L117" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
@@ -9353,7 +9413,11 @@
           <t>[UNVERIFIED] — verify</t>
         </is>
       </c>
-      <c r="P117" s="2" t="inlineStr"/>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -9431,7 +9495,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -9489,9 +9553,9 @@
           <t>claudiovarani@fondotelemaco.it / c.varani70@gmail.com  (found on linked in)</t>
         </is>
       </c>
-      <c r="L119" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L119" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
@@ -9509,7 +9573,11 @@
           <t>[UNVERIFIED] — verify FIA stance</t>
         </is>
       </c>
-      <c r="P119" s="2" t="inlineStr"/>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -9645,9 +9713,9 @@
           <t>fabio.cappuccio@previmoda.it</t>
         </is>
       </c>
-      <c r="L121" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L121" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
@@ -9665,7 +9733,11 @@
           <t>[UNVERIFIED] — verify Economia Reale membership</t>
         </is>
       </c>
-      <c r="P121" s="2" t="inlineStr"/>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -9721,9 +9793,9 @@
           <t>andrea.laruccia@previbank.it</t>
         </is>
       </c>
-      <c r="L122" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L122" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
@@ -9741,7 +9813,11 @@
           <t>[UNVERIFIED] — verify</t>
         </is>
       </c>
-      <c r="P122" s="2" t="inlineStr"/>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -9797,9 +9873,9 @@
           <t>d.ballarin@prevedi.it</t>
         </is>
       </c>
-      <c r="L123" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L123" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
@@ -9817,7 +9893,11 @@
           <t>[UNVERIFIED] — verify FIA stance</t>
         </is>
       </c>
-      <c r="P123" s="2" t="inlineStr"/>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -9873,9 +9953,9 @@
           <t>marco@prevaer.it</t>
         </is>
       </c>
-      <c r="L124" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L124" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
@@ -9893,7 +9973,11 @@
           <t>[UNVERIFIED] — verify membership</t>
         </is>
       </c>
-      <c r="P124" s="2" t="inlineStr"/>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -9949,9 +10033,9 @@
           <t>riccardor@fondoperseosirio.it</t>
         </is>
       </c>
-      <c r="L125" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L125" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
@@ -9969,7 +10053,11 @@
           <t>[UNVERIFIED] — public-sector caution</t>
         </is>
       </c>
-      <c r="P125" s="2" t="inlineStr"/>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -10105,9 +10193,9 @@
           <t>s.mirenghi@fondosanita.it</t>
         </is>
       </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L127" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
@@ -10125,7 +10213,11 @@
           <t>[UNVERIFIED] — verify</t>
         </is>
       </c>
-      <c r="P127" s="2" t="inlineStr"/>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -10181,9 +10273,9 @@
           <t>spierini@fondoeurofer.it</t>
         </is>
       </c>
-      <c r="L128" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L128" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
@@ -10201,7 +10293,11 @@
           <t>[UNVERIFIED] — verify</t>
         </is>
       </c>
-      <c r="P128" s="2" t="inlineStr"/>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -10257,9 +10353,9 @@
           <t>fondoposte@fondoposte.it</t>
         </is>
       </c>
-      <c r="L129" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L129" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
@@ -10277,7 +10373,11 @@
           <t>[UNVERIFIED] — UNGATED — DG Metta + published fund address (fondoposte.it) — replaced wrong-desk import contact (Del Fante = Poste group CEO) — new president Antonio Nervi, board mandate to Bilancio 2025</t>
         </is>
       </c>
-      <c r="P129" s="2" t="inlineStr"/>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -10333,9 +10433,9 @@
           <t>massimiliano.spadari@fondogommaplastica.it</t>
         </is>
       </c>
-      <c r="L130" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L130" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
@@ -10353,7 +10453,11 @@
           <t>[UNVERIFIED] — verify Economia Reale membership</t>
         </is>
       </c>
-      <c r="P130" s="2" t="inlineStr"/>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -10409,9 +10513,9 @@
           <t>james.giovanardi@foncer.it</t>
         </is>
       </c>
-      <c r="L131" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L131" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
@@ -10429,7 +10533,11 @@
           <t>[UNVERIFIED] — verify membership</t>
         </is>
       </c>
-      <c r="P131" s="2" t="inlineStr"/>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -10485,9 +10593,9 @@
           <t>budassi@previdenzacooperativa.it</t>
         </is>
       </c>
-      <c r="L132" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L132" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
@@ -10505,7 +10613,11 @@
           <t>[UNVERIFIED] — verify</t>
         </is>
       </c>
-      <c r="P132" s="2" t="inlineStr"/>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -10561,9 +10673,9 @@
           <t>a.gentile@fondobyblos.it</t>
         </is>
       </c>
-      <c r="L133" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L133" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
@@ -10581,7 +10693,11 @@
           <t>[UNVERIFIED] — verify</t>
         </is>
       </c>
-      <c r="P133" s="2" t="inlineStr"/>
+      <c r="P133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -10704,7 +10820,7 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>Artur Trela</t>
+          <t>Andrzej Sołdek</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
@@ -10714,7 +10830,7 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>FIND: artur.trela@pzu.pl (group pattern)</t>
+          <t>Andrzej.Sołdek@pzu.pl</t>
         </is>
       </c>
       <c r="L135" s="8" t="inlineStr">
@@ -10734,7 +10850,7 @@
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>[UNVERIFIED] — UNGATED — new right desk: Trela is ex-PZU Managing Director for Investments — 2026 group restructuring emphasises alternative and infrastructure investments (pzu.pl/bank.pl)</t>
+          <t>[CONFIRMED] — address confirmed 2026-08-03 by Michal from the actual send. Supersedes the unverified group-pattern guess artur.trela@pzu.pl.</t>
         </is>
       </c>
       <c r="P135" s="2" t="inlineStr">
@@ -10797,9 +10913,9 @@
           <t>jaroslaw.parkot@warta.pl</t>
         </is>
       </c>
-      <c r="L136" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L136" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
@@ -10817,7 +10933,11 @@
           <t>[UNVERIFIED] — CLUSTER→Talanx (no pipeline lead) — verify local discretion</t>
         </is>
       </c>
-      <c r="P136" s="2" t="inlineStr"/>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -10873,9 +10993,9 @@
           <t>tomasz.krzaczkowski@allianz.pl</t>
         </is>
       </c>
-      <c r="L137" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L137" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
@@ -10893,7 +11013,11 @@
           <t>[UNVERIFIED] — CLUSTER→allianz-pensionskasse-ag — AIM-framed</t>
         </is>
       </c>
-      <c r="P137" s="2" t="inlineStr"/>
+      <c r="P137" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -10949,9 +11073,9 @@
           <t>roger.hodgkiss@generali.pl</t>
         </is>
       </c>
-      <c r="L138" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L138" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
@@ -11025,9 +11149,9 @@
           <t>anna.wlodarczyk-moczkowska@compensa.pl</t>
         </is>
       </c>
-      <c r="L139" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L139" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
@@ -11101,9 +11225,9 @@
           <t>piotr.narloch@interrisk.pl</t>
         </is>
       </c>
-      <c r="L140" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L140" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
@@ -11229,9 +11353,9 @@
           <t>jaroslaw.matusiewicz@tuz.pl</t>
         </is>
       </c>
-      <c r="L142" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L142" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
@@ -11305,9 +11429,9 @@
           <t>sudzinska.grazyna@link4.pl</t>
         </is>
       </c>
-      <c r="L143" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L143" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
@@ -11381,9 +11505,9 @@
           <t>mariusz.kurowski@benefia.pl</t>
         </is>
       </c>
-      <c r="L144" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L144" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
@@ -11457,9 +11581,9 @@
           <t>artur.borowinski@ergohestia.pl</t>
         </is>
       </c>
-      <c r="L145" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L145" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
@@ -11477,7 +11601,11 @@
           <t>[UNVERIFIED] — CLUSTER→MEAG (no pipeline lead) — MEAG-managed — import name typo fixed (Borowiński)</t>
         </is>
       </c>
-      <c r="P145" s="2" t="inlineStr"/>
+      <c r="P145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -11609,9 +11737,9 @@
           <t>bbanaskiewicz@polisa-zycie.pl</t>
         </is>
       </c>
-      <c r="L147" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L147" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
@@ -12405,9 +12533,9 @@
           <t>virgil.soncutean@allianztiriac.ro</t>
         </is>
       </c>
-      <c r="L158" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L158" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
@@ -12425,7 +12553,11 @@
           <t>[UNVERIFIED] — market leader — pairs with AZT row</t>
         </is>
       </c>
-      <c r="P158" s="2" t="inlineStr"/>
+      <c r="P158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -12481,9 +12613,9 @@
           <t>calin.matei@groupama.ro</t>
         </is>
       </c>
-      <c r="L159" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L159" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
@@ -12501,7 +12633,11 @@
           <t>[UNVERIFIED] — Paris-framed</t>
         </is>
       </c>
-      <c r="P159" s="2" t="inlineStr"/>
+      <c r="P159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -12557,9 +12693,9 @@
           <t>adrian.marin@generali.ro</t>
         </is>
       </c>
-      <c r="L160" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L160" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
@@ -12633,9 +12769,9 @@
           <t>madalin.rosu@asirom.ro</t>
         </is>
       </c>
-      <c r="L161" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L161" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
@@ -12709,9 +12845,9 @@
           <t>mihai.tecau@omniasig.ro</t>
         </is>
       </c>
-      <c r="L162" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L162" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
@@ -12785,9 +12921,9 @@
           <t>mesut.yetiskul@signal-iduna.ro</t>
         </is>
       </c>
-      <c r="L163" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L163" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
@@ -12937,9 +13073,9 @@
           <t>dragos-marius.calin@grawe.ro</t>
         </is>
       </c>
-      <c r="L165" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L165" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M165" s="2" t="inlineStr">
@@ -13013,9 +13149,9 @@
           <t>kuldeep.kaushik@nn.ro</t>
         </is>
       </c>
-      <c r="L166" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L166" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
@@ -13033,7 +13169,11 @@
           <t>[UNVERIFIED] — life leader — import contact name had spelling variants</t>
         </is>
       </c>
-      <c r="P166" s="2" t="inlineStr"/>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -13089,9 +13229,9 @@
           <t>stavrositus@bcrasigviata.ro</t>
         </is>
       </c>
-      <c r="L167" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L167" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
@@ -13187,7 +13327,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -13245,9 +13385,9 @@
           <t>anita@eurolife-asigurari.ro</t>
         </is>
       </c>
-      <c r="L169" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L169" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
@@ -13567,7 +13707,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -13625,9 +13765,9 @@
           <t>raluca.morar@brd.ro</t>
         </is>
       </c>
-      <c r="L174" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L174" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
@@ -13645,7 +13785,11 @@
           <t>[UNVERIFIED] — verification-first</t>
         </is>
       </c>
-      <c r="P174" s="2" t="inlineStr"/>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -13781,9 +13925,9 @@
           <t>adrian.negru@raiffeisen.ro</t>
         </is>
       </c>
-      <c r="L176" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L176" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr">
@@ -13857,9 +14001,9 @@
           <t>anne-marie.mancas@generali.ro</t>
         </is>
       </c>
-      <c r="L177" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L177" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M177" s="2" t="inlineStr">
@@ -13877,7 +14021,11 @@
           <t>[UNVERIFIED] — fund name is Aripi — verify AUM</t>
         </is>
       </c>
-      <c r="P177" s="2" t="inlineStr"/>
+      <c r="P177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -13933,9 +14081,9 @@
           <t>marius.ratiu@carpathiapensii.ro</t>
         </is>
       </c>
-      <c r="L178" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L178" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr">
@@ -14009,9 +14157,9 @@
           <t>corina@btpensii.ro</t>
         </is>
       </c>
-      <c r="L179" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L179" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M179" s="2" t="inlineStr">
@@ -14085,9 +14233,9 @@
           <t>dan.sucu@confederatia-concordia.ro</t>
         </is>
       </c>
-      <c r="L180" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L180" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr"/>
@@ -14157,9 +14305,9 @@
           <t>blaz.hribar@pd-a.si</t>
         </is>
       </c>
-      <c r="L181" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L181" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M181" s="2" t="inlineStr">
@@ -14441,9 +14589,9 @@
           <t>gregor.rovansek@prva.si</t>
         </is>
       </c>
-      <c r="L185" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L185" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M185" s="2" t="inlineStr">
@@ -14597,9 +14745,9 @@
           <t>saso.smigic@generali-investments.si</t>
         </is>
       </c>
-      <c r="L187" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L187" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M187" s="2" t="inlineStr">
@@ -14673,9 +14821,9 @@
           <t>andrej@sava-pokojninska.si</t>
         </is>
       </c>
-      <c r="L188" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L188" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M188" s="2" t="inlineStr">
@@ -14749,9 +14897,9 @@
           <t>aljosha.urshic@triglav.si</t>
         </is>
       </c>
-      <c r="L189" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L189" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M189" s="2" t="inlineStr">
@@ -14905,9 +15053,9 @@
           <t>vanja.horvat@generali.com</t>
         </is>
       </c>
-      <c r="L191" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L191" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M191" s="2" t="inlineStr">
@@ -14981,9 +15129,9 @@
           <t>david.kastelic@grawe.si</t>
         </is>
       </c>
-      <c r="L192" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L192" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M192" s="2" t="inlineStr">
@@ -15133,9 +15281,9 @@
           <t>natasa.hajdinjak@prva.si</t>
         </is>
       </c>
-      <c r="L194" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L194" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M194" s="2" t="inlineStr">
@@ -15273,9 +15421,9 @@
           <t>barbara.smolnikar@zav-vita.si</t>
         </is>
       </c>
-      <c r="L196" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L196" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M196" s="2" t="inlineStr">
@@ -17061,9 +17209,9 @@
           <t>dario.scannapieco@cdp.it</t>
         </is>
       </c>
-      <c r="L220" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L220" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M220" s="2" t="inlineStr">
@@ -17137,9 +17285,9 @@
           <t>reinis.berzins@altum.lv</t>
         </is>
       </c>
-      <c r="L221" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L221" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M221" s="2" t="inlineStr">
@@ -17289,9 +17437,9 @@
           <t>n.calvino@eib.org</t>
         </is>
       </c>
-      <c r="L223" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L223" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M223" s="2" t="inlineStr">
@@ -17513,9 +17661,9 @@
           <t>manuel.munoz@ico.es</t>
         </is>
       </c>
-      <c r="L226" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L226" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M226" s="2" t="inlineStr">
@@ -17733,9 +17881,9 @@
           <t>jost.dolnicar@zav-sava.si</t>
         </is>
       </c>
-      <c r="L229" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L229" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M229" s="2" t="inlineStr">
@@ -18900,9 +19048,9 @@
           <t>nino.pavic@adriatic-osiguranje.hr</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -18976,9 +19124,9 @@
           <t>jakovacm@allianz.hr</t>
         </is>
       </c>
-      <c r="L16" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -18996,7 +19144,11 @@
           <t>[CONFIRMED] — CLUSTER→allianz-pensionskasse-ag — coordinate with Allianz group rows — Matić (Allianz Österreich CEO) previously ran Allianz Croatia</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -19052,9 +19204,9 @@
           <t>trendic@wiener.at</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -19072,7 +19224,11 @@
           <t>[UNVERIFIED] — subsidiary of VIG — coordinate with VIG row — email domain wiener.at (group address)</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -19128,9 +19284,9 @@
           <t>natasa.kapetanovic@grawe.hr</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -19204,9 +19360,9 @@
           <t>mario.carini@generali.hr</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -19280,9 +19436,9 @@
           <t>tedo.djekanovic@triglav.hr</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -19356,9 +19512,9 @@
           <t>marko.klemencic@merkur.hr</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -20412,9 +20568,9 @@
           <t>d.mazarakis@ethnikiasfalistiki.gr</t>
         </is>
       </c>
-      <c r="L35" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -20432,7 +20588,11 @@
           <t>[UNVERIFIED] — verify ownership status (reported Piraeus talks) before approach</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -20488,9 +20648,9 @@
           <t>kantorosy@interamerican.gr</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -20508,7 +20668,11 @@
           <t>[UNVERIFIED] — group-framed</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -20564,9 +20728,9 @@
           <t>fekih@groupama.gr</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -20712,9 +20876,9 @@
           <t>panos.dimitriou@generali.gr</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -20732,7 +20896,11 @@
           <t>[UNVERIFIED] — shares contact with AXA Greece duplicate row — one email max</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -20984,9 +21152,9 @@
           <t>kaskarelis@ydrogios.gr</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L43" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -21060,9 +21228,9 @@
           <t>ivotsaridis@interlife.gr</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L44" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -21360,9 +21528,9 @@
           <t>mihaly.erdos@generali.hu</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L48" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -21436,9 +21604,9 @@
           <t>bacso.gergely@allianz.hu</t>
         </is>
       </c>
-      <c r="L49" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L49" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -21456,7 +21624,11 @@
           <t>[UNVERIFIED] — CLUSTER→allianz-pensionskasse-ag — market leader — AIM framing</t>
         </is>
       </c>
-      <c r="P49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -21512,9 +21684,9 @@
           <t>alexandre.jeanjean@groupama.hu</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L50" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -21588,9 +21760,9 @@
           <t>havas.gabor@union.hu</t>
         </is>
       </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L51" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -21812,9 +21984,9 @@
           <t>istvan@cigpannonia.hu</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L54" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -22188,9 +22360,9 @@
           <t>barna.zsolt@mbhbank.hu</t>
         </is>
       </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L59" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -22264,9 +22436,9 @@
           <t>kovacs.zsolt@mpb.hu</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -22340,9 +22512,9 @@
           <t>wilfried-kempchen.daniel@signal.hu</t>
         </is>
       </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -22416,9 +22588,9 @@
           <t>spadlo-kolano@metlife.hu</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L62" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -22564,17 +22736,17 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>CIO</t>
+          <t>Chief Investment Officer, Unipol Gruppo and UnipolSai</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>baudir@pec.unipol.it</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+          <t>investor.relations@unipol.it</t>
+        </is>
+      </c>
+      <c r="L64" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -22589,7 +22761,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>[UNVERIFIED] — GATED(fit 56) — import email is PEC certified-mail — find standard address</t>
+          <t>[LIKELY] — Baudi confirmed as CIO (Bloomberg, MarketScreener). Published IR inbox used: the only address on file was a PEC (certified legal mail), wrong channel for outreach. No verifiable direct address. Gianluca Banfi (Head of Alternative Investments, UnipolSai) is a better desk-level target.</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr"/>
@@ -22648,9 +22820,9 @@
           <t>alberto.vacca@allianz.it</t>
         </is>
       </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L65" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -22668,7 +22840,11 @@
           <t>[UNVERIFIED] — CLUSTER→allianz-pensionskasse-ag — AIM-framed</t>
         </is>
       </c>
-      <c r="P65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -22804,9 +22980,9 @@
           <t>virginia.borla@intesasanpaolo.com</t>
         </is>
       </c>
-      <c r="L67" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L67" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -22824,7 +23000,11 @@
           <t>[UNVERIFIED] — verify Borla remit</t>
         </is>
       </c>
-      <c r="P67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -22880,9 +23060,9 @@
           <t>psemenzato@zurich.it</t>
         </is>
       </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L68" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -22956,9 +23136,9 @@
           <t>stephan@hdiassicurazioni.it</t>
         </is>
       </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L69" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -23032,9 +23212,9 @@
           <t>signorinimarco@helvetia.it</t>
         </is>
       </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L70" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -23108,9 +23288,9 @@
           <t>marco.nostini@nobisassicurazioni.it</t>
         </is>
       </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L71" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -23247,7 +23427,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Artur Trela</t>
+          <t>Andrzej Sołdek</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -23257,7 +23437,7 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>FIND: artur.trela@pzu.pl (group pattern)</t>
+          <t>Andrzej.Sołdek@pzu.pl</t>
         </is>
       </c>
       <c r="L73" s="8" t="inlineStr">
@@ -23277,7 +23457,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>[UNVERIFIED] — UNGATED — new right desk: Trela is ex-PZU Managing Director for Investments — 2026 group restructuring emphasises alternative and infrastructure investments (pzu.pl/bank.pl)</t>
+          <t>[CONFIRMED] — address confirmed 2026-08-03 by Michal from the actual send. Supersedes the unverified group-pattern guess artur.trela@pzu.pl.</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -23340,9 +23520,9 @@
           <t>jaroslaw.parkot@warta.pl</t>
         </is>
       </c>
-      <c r="L74" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L74" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -23360,7 +23540,11 @@
           <t>[UNVERIFIED] — CLUSTER→Talanx (no pipeline lead) — verify local discretion</t>
         </is>
       </c>
-      <c r="P74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -23416,9 +23600,9 @@
           <t>tomasz.krzaczkowski@allianz.pl</t>
         </is>
       </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L75" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -23436,7 +23620,11 @@
           <t>[UNVERIFIED] — CLUSTER→allianz-pensionskasse-ag — AIM-framed</t>
         </is>
       </c>
-      <c r="P75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -23492,9 +23680,9 @@
           <t>roger.hodgkiss@generali.pl</t>
         </is>
       </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L76" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -23568,9 +23756,9 @@
           <t>anna.wlodarczyk-moczkowska@compensa.pl</t>
         </is>
       </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -23644,9 +23832,9 @@
           <t>piotr.narloch@interrisk.pl</t>
         </is>
       </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L78" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -23772,9 +23960,9 @@
           <t>jaroslaw.matusiewicz@tuz.pl</t>
         </is>
       </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L80" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -23848,9 +24036,9 @@
           <t>sudzinska.grazyna@link4.pl</t>
         </is>
       </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L81" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -23924,9 +24112,9 @@
           <t>mariusz.kurowski@benefia.pl</t>
         </is>
       </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L82" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -24000,9 +24188,9 @@
           <t>artur.borowinski@ergohestia.pl</t>
         </is>
       </c>
-      <c r="L83" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L83" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -24020,7 +24208,11 @@
           <t>[UNVERIFIED] — CLUSTER→MEAG (no pipeline lead) — MEAG-managed — import name typo fixed (Borowiński)</t>
         </is>
       </c>
-      <c r="P83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -24152,9 +24344,9 @@
           <t>bbanaskiewicz@polisa-zycie.pl</t>
         </is>
       </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L85" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -24228,9 +24420,9 @@
           <t>virgil.soncutean@allianztiriac.ro</t>
         </is>
       </c>
-      <c r="L86" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L86" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -24248,7 +24440,11 @@
           <t>[UNVERIFIED] — market leader — pairs with AZT row</t>
         </is>
       </c>
-      <c r="P86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -24304,9 +24500,9 @@
           <t>calin.matei@groupama.ro</t>
         </is>
       </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L87" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -24324,7 +24520,11 @@
           <t>[UNVERIFIED] — Paris-framed</t>
         </is>
       </c>
-      <c r="P87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -24380,9 +24580,9 @@
           <t>adrian.marin@generali.ro</t>
         </is>
       </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L88" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -24456,9 +24656,9 @@
           <t>madalin.rosu@asirom.ro</t>
         </is>
       </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L89" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -24532,9 +24732,9 @@
           <t>mihai.tecau@omniasig.ro</t>
         </is>
       </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L90" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -24608,9 +24808,9 @@
           <t>mesut.yetiskul@signal-iduna.ro</t>
         </is>
       </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L91" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -24760,9 +24960,9 @@
           <t>dragos-marius.calin@grawe.ro</t>
         </is>
       </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L93" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -24836,9 +25036,9 @@
           <t>kuldeep.kaushik@nn.ro</t>
         </is>
       </c>
-      <c r="L94" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L94" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -24856,7 +25056,11 @@
           <t>[UNVERIFIED] — life leader — import contact name had spelling variants</t>
         </is>
       </c>
-      <c r="P94" s="2" t="inlineStr"/>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -24912,9 +25116,9 @@
           <t>stavrositus@bcrasigviata.ro</t>
         </is>
       </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L95" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -25010,7 +25214,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -25068,9 +25272,9 @@
           <t>anita@eurolife-asigurari.ro</t>
         </is>
       </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L97" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -25288,9 +25492,9 @@
           <t>vanja.horvat@generali.com</t>
         </is>
       </c>
-      <c r="L100" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L100" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -25364,9 +25568,9 @@
           <t>david.kastelic@grawe.si</t>
         </is>
       </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L101" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -25516,9 +25720,9 @@
           <t>natasa.hajdinjak@prva.si</t>
         </is>
       </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L103" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -25656,9 +25860,9 @@
           <t>barbara.smolnikar@zav-vita.si</t>
         </is>
       </c>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L105" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
@@ -26752,9 +26956,9 @@
           <t>dario.scannapieco@cdp.it</t>
         </is>
       </c>
-      <c r="L120" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L120" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
@@ -26828,9 +27032,9 @@
           <t>reinis.berzins@altum.lv</t>
         </is>
       </c>
-      <c r="L121" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L121" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
@@ -26980,9 +27184,9 @@
           <t>n.calvino@eib.org</t>
         </is>
       </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L123" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
@@ -27204,9 +27408,9 @@
           <t>manuel.munoz@ico.es</t>
         </is>
       </c>
-      <c r="L126" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L126" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
@@ -27424,9 +27628,9 @@
           <t>jost.dolnicar@zav-sava.si</t>
         </is>
       </c>
-      <c r="L129" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L129" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
@@ -28491,9 +28695,9 @@
           <t>kristijan.buk@azfond.hr</t>
         </is>
       </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -28567,9 +28771,9 @@
           <t>ekomunikacija@pbzco-fond.hr</t>
         </is>
       </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -28587,7 +28791,11 @@
           <t>[LIKELY] — UNGATED — entity VERIFIED: PBZ Croatia osiguranje d.d. (pbzco-fond.hr) — board: Marić (president), Goran Kralj — published contact channel — confirmed PE/VC LP interests (South Central Ventures, Prosperus)</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -28643,9 +28851,9 @@
           <t>gordan.sumanovic@rmf.hr</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -28719,9 +28927,9 @@
           <t>kristijan.buk@azfond.hr</t>
         </is>
       </c>
-      <c r="L17" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -29031,9 +29239,9 @@
           <t>radojka.hainski@crosig.hr</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -29051,7 +29259,11 @@
           <t>[UNVERIFIED] — same Adris/CO group as Croatia osiguranje d.d. — fold into the group conversation</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -29263,9 +29475,9 @@
           <t>thompolouse@interamerican.gr</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -29411,9 +29623,9 @@
           <t>knebis@cosmote.gr</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -29559,9 +29771,9 @@
           <t>tamas.marusinecz@allianz.hu</t>
         </is>
       </c>
-      <c r="L28" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -29579,7 +29791,11 @@
           <t>[UNVERIFIED] — no email in import</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -29787,9 +30003,9 @@
           <t>tamas@mbhnyp.hu</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -29863,9 +30079,9 @@
           <t>marta.hanak@aranykornyp.hu</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -29883,7 +30099,11 @@
           <t>[UNVERIFIED] — no email in import</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -29939,9 +30159,9 @@
           <t>timea.pataki@horizontpenztar.hu</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
@@ -29959,7 +30179,11 @@
           <t>[UNVERIFIED] — largest surviving magannyugdijpenztar — verify AUM via MNB</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -30015,9 +30239,9 @@
           <t>poda.jeno@hnyp.hu</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -30091,9 +30315,9 @@
           <t>tohai.szilvia@vnyp.hu</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -30327,9 +30551,9 @@
           <t>riccardo.resciniti@fondoespero.it</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -30347,7 +30571,11 @@
           <t>[UNVERIFIED] — public-sector caution</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -30425,7 +30653,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -30643,9 +30871,9 @@
           <t>matteo.colamussi@fondopriamo.it</t>
         </is>
       </c>
-      <c r="L42" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -30663,7 +30891,11 @@
           <t>[UNVERIFIED] — verify FIA stance</t>
         </is>
       </c>
-      <c r="P42" s="2" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -30847,9 +31079,9 @@
           <t>sabina.valentini@filcoopsanitario.it</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L45" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -30923,9 +31155,9 @@
           <t>fabio.barigazzi@alifond.it</t>
         </is>
       </c>
-      <c r="L46" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -30943,7 +31175,11 @@
           <t>[UNVERIFIED] — verify</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -31021,7 +31257,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -31079,9 +31315,9 @@
           <t>claudiovarani@fondotelemaco.it / c.varani70@gmail.com  (found on linked in)</t>
         </is>
       </c>
-      <c r="L48" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L48" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -31099,7 +31335,11 @@
           <t>[UNVERIFIED] — verify FIA stance</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -31235,9 +31475,9 @@
           <t>fabio.cappuccio@previmoda.it</t>
         </is>
       </c>
-      <c r="L50" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -31255,7 +31495,11 @@
           <t>[UNVERIFIED] — verify Economia Reale membership</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -31311,9 +31555,9 @@
           <t>andrea.laruccia@previbank.it</t>
         </is>
       </c>
-      <c r="L51" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L51" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -31331,7 +31575,11 @@
           <t>[UNVERIFIED] — verify</t>
         </is>
       </c>
-      <c r="P51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -31387,9 +31635,9 @@
           <t>d.ballarin@prevedi.it</t>
         </is>
       </c>
-      <c r="L52" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L52" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -31407,7 +31655,11 @@
           <t>[UNVERIFIED] — verify FIA stance</t>
         </is>
       </c>
-      <c r="P52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -31463,9 +31715,9 @@
           <t>marco@prevaer.it</t>
         </is>
       </c>
-      <c r="L53" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L53" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -31483,7 +31735,11 @@
           <t>[UNVERIFIED] — verify membership</t>
         </is>
       </c>
-      <c r="P53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -31539,9 +31795,9 @@
           <t>riccardor@fondoperseosirio.it</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L54" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -31559,7 +31815,11 @@
           <t>[UNVERIFIED] — public-sector caution</t>
         </is>
       </c>
-      <c r="P54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -31695,9 +31955,9 @@
           <t>s.mirenghi@fondosanita.it</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L56" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -31715,7 +31975,11 @@
           <t>[UNVERIFIED] — verify</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -31771,9 +32035,9 @@
           <t>spierini@fondoeurofer.it</t>
         </is>
       </c>
-      <c r="L57" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L57" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -31791,7 +32055,11 @@
           <t>[UNVERIFIED] — verify</t>
         </is>
       </c>
-      <c r="P57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -31847,9 +32115,9 @@
           <t>fondoposte@fondoposte.it</t>
         </is>
       </c>
-      <c r="L58" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L58" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -31867,7 +32135,11 @@
           <t>[UNVERIFIED] — UNGATED — DG Metta + published fund address (fondoposte.it) — replaced wrong-desk import contact (Del Fante = Poste group CEO) — new president Antonio Nervi, board mandate to Bilancio 2025</t>
         </is>
       </c>
-      <c r="P58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -31923,9 +32195,9 @@
           <t>massimiliano.spadari@fondogommaplastica.it</t>
         </is>
       </c>
-      <c r="L59" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L59" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -31943,7 +32215,11 @@
           <t>[UNVERIFIED] — verify Economia Reale membership</t>
         </is>
       </c>
-      <c r="P59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -31999,9 +32275,9 @@
           <t>james.giovanardi@foncer.it</t>
         </is>
       </c>
-      <c r="L60" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L60" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -32019,7 +32295,11 @@
           <t>[UNVERIFIED] — verify membership</t>
         </is>
       </c>
-      <c r="P60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -32075,9 +32355,9 @@
           <t>budassi@previdenzacooperativa.it</t>
         </is>
       </c>
-      <c r="L61" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L61" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -32095,7 +32375,11 @@
           <t>[UNVERIFIED] — verify</t>
         </is>
       </c>
-      <c r="P61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -32151,9 +32435,9 @@
           <t>a.gentile@fondobyblos.it</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L62" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -32171,7 +32455,11 @@
           <t>[UNVERIFIED] — verify</t>
         </is>
       </c>
-      <c r="P62" s="2" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -33209,7 +33497,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -33267,9 +33555,9 @@
           <t>raluca.morar@brd.ro</t>
         </is>
       </c>
-      <c r="L77" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L77" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -33287,7 +33575,11 @@
           <t>[UNVERIFIED] — verification-first</t>
         </is>
       </c>
-      <c r="P77" s="2" t="inlineStr"/>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -33423,9 +33715,9 @@
           <t>adrian.negru@raiffeisen.ro</t>
         </is>
       </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L79" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -33499,9 +33791,9 @@
           <t>anne-marie.mancas@generali.ro</t>
         </is>
       </c>
-      <c r="L80" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L80" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -33519,7 +33811,11 @@
           <t>[UNVERIFIED] — fund name is Aripi — verify AUM</t>
         </is>
       </c>
-      <c r="P80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -33575,9 +33871,9 @@
           <t>marius.ratiu@carpathiapensii.ro</t>
         </is>
       </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L81" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -33651,9 +33947,9 @@
           <t>corina@btpensii.ro</t>
         </is>
       </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L82" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -33727,9 +34023,9 @@
           <t>dan.sucu@confederatia-concordia.ro</t>
         </is>
       </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L83" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr"/>
@@ -33799,9 +34095,9 @@
           <t>blaz.hribar@pd-a.si</t>
         </is>
       </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L84" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -34083,9 +34379,9 @@
           <t>gregor.rovansek@prva.si</t>
         </is>
       </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L88" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -34239,9 +34535,9 @@
           <t>saso.smigic@generali-investments.si</t>
         </is>
       </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L90" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -34315,9 +34611,9 @@
           <t>andrej@sava-pokojninska.si</t>
         </is>
       </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L91" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -34391,9 +34687,9 @@
           <t>aljosha.urshic@triglav.si</t>
         </is>
       </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L92" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -35418,9 +35714,9 @@
           <t>nino.pavic@adriatic-osiguranje.hr</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -35494,9 +35790,9 @@
           <t>jakovacm@allianz.hr</t>
         </is>
       </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -35514,7 +35810,11 @@
           <t>[CONFIRMED] — CLUSTER→allianz-pensionskasse-ag — coordinate with Allianz group rows — Matić (Allianz Österreich CEO) previously ran Allianz Croatia</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -35570,9 +35870,9 @@
           <t>trendic@wiener.at</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -35590,7 +35890,11 @@
           <t>[UNVERIFIED] — subsidiary of VIG — coordinate with VIG row — email domain wiener.at (group address)</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -35646,9 +35950,9 @@
           <t>natasa.kapetanovic@grawe.hr</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -35722,9 +36026,9 @@
           <t>mario.carini@generali.hr</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -35798,9 +36102,9 @@
           <t>tedo.djekanovic@triglav.hr</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -35874,9 +36178,9 @@
           <t>marko.klemencic@merkur.hr</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -35950,9 +36254,9 @@
           <t>kristijan.buk@azfond.hr</t>
         </is>
       </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -36026,9 +36330,9 @@
           <t>ekomunikacija@pbzco-fond.hr</t>
         </is>
       </c>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -36046,7 +36350,11 @@
           <t>[LIKELY] — UNGATED — entity VERIFIED: PBZ Croatia osiguranje d.d. (pbzco-fond.hr) — board: Marić (president), Goran Kralj — published contact channel — confirmed PE/VC LP interests (South Central Ventures, Prosperus)</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -36102,9 +36410,9 @@
           <t>gordan.sumanovic@rmf.hr</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -36178,9 +36486,9 @@
           <t>kristijan.buk@azfond.hr</t>
         </is>
       </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>research</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -36490,9 +36798,9 @@
           <t>radojka.hainski@crosig.hr</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -36510,7 +36818,11 @@
           <t>[UNVERIFIED] — same Adris/CO group as Croatia osiguranje d.d. — fold into the group conversation</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -36566,9 +36878,9 @@
           <t>d.mazarakis@ethnikiasfalistiki.gr</t>
         </is>
       </c>
-      <c r="L19" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -36586,7 +36898,11 @@
           <t>[UNVERIFIED] — verify ownership status (reported Piraeus talks) before approach</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -36642,9 +36958,9 @@
           <t>kantorosy@interamerican.gr</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -36662,7 +36978,11 @@
           <t>[UNVERIFIED] — group-framed</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -36718,9 +37038,9 @@
           <t>fekih@groupama.gr</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -36866,9 +37186,9 @@
           <t>panos.dimitriou@generali.gr</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -36886,7 +37206,11 @@
           <t>[UNVERIFIED] — shares contact with AXA Greece duplicate row — one email max</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -37138,9 +37462,9 @@
           <t>kaskarelis@ydrogios.gr</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -37214,9 +37538,9 @@
           <t>ivotsaridis@interlife.gr</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -37514,9 +37838,9 @@
           <t>thompolouse@interamerican.gr</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -37662,9 +37986,9 @@
           <t>knebis@cosmote.gr</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -37810,9 +38134,9 @@
           <t>mihaly.erdos@generali.hu</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -37886,9 +38210,9 @@
           <t>bacso.gergely@allianz.hu</t>
         </is>
       </c>
-      <c r="L37" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -37906,7 +38230,11 @@
           <t>[UNVERIFIED] — CLUSTER→allianz-pensionskasse-ag — market leader — AIM framing</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -37962,9 +38290,9 @@
           <t>alexandre.jeanjean@groupama.hu</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L38" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -38038,9 +38366,9 @@
           <t>havas.gabor@union.hu</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -38262,9 +38590,9 @@
           <t>istvan@cigpannonia.hu</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L42" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -38638,9 +38966,9 @@
           <t>barna.zsolt@mbhbank.hu</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L47" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -38714,9 +39042,9 @@
           <t>kovacs.zsolt@mpb.hu</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L48" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -38790,9 +39118,9 @@
           <t>wilfried-kempchen.daniel@signal.hu</t>
         </is>
       </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -38866,9 +39194,9 @@
           <t>spadlo-kolano@metlife.hu</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L50" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -38942,9 +39270,9 @@
           <t>tamas.marusinecz@allianz.hu</t>
         </is>
       </c>
-      <c r="L51" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L51" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -38962,7 +39290,11 @@
           <t>[UNVERIFIED] — no email in import</t>
         </is>
       </c>
-      <c r="P51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -39170,9 +39502,9 @@
           <t>tamas@mbhnyp.hu</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L54" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -39246,9 +39578,9 @@
           <t>marta.hanak@aranykornyp.hu</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L55" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -39266,7 +39598,11 @@
           <t>[UNVERIFIED] — no email in import</t>
         </is>
       </c>
-      <c r="P55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -39322,9 +39658,9 @@
           <t>timea.pataki@horizontpenztar.hu</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L56" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -39342,7 +39678,11 @@
           <t>[UNVERIFIED] — largest surviving magannyugdijpenztar — verify AUM via MNB</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -39398,9 +39738,9 @@
           <t>poda.jeno@hnyp.hu</t>
         </is>
       </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L57" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -39474,9 +39814,9 @@
           <t>tohai.szilvia@vnyp.hu</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L58" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -39622,17 +39962,17 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>CIO</t>
+          <t>Chief Investment Officer, Unipol Gruppo and UnipolSai</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>baudir@pec.unipol.it</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+          <t>investor.relations@unipol.it</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -39647,7 +39987,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>[UNVERIFIED] — GATED(fit 56) — import email is PEC certified-mail — find standard address</t>
+          <t>[LIKELY] — Baudi confirmed as CIO (Bloomberg, MarketScreener). Published IR inbox used: the only address on file was a PEC (certified legal mail), wrong channel for outreach. No verifiable direct address. Gianluca Banfi (Head of Alternative Investments, UnipolSai) is a better desk-level target.</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr"/>
@@ -39706,9 +40046,9 @@
           <t>alberto.vacca@allianz.it</t>
         </is>
       </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L61" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -39726,7 +40066,11 @@
           <t>[UNVERIFIED] — CLUSTER→allianz-pensionskasse-ag — AIM-framed</t>
         </is>
       </c>
-      <c r="P61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -39862,9 +40206,9 @@
           <t>virginia.borla@intesasanpaolo.com</t>
         </is>
       </c>
-      <c r="L63" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L63" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -39882,7 +40226,11 @@
           <t>[UNVERIFIED] — verify Borla remit</t>
         </is>
       </c>
-      <c r="P63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -39938,9 +40286,9 @@
           <t>psemenzato@zurich.it</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L64" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -40014,9 +40362,9 @@
           <t>stephan@hdiassicurazioni.it</t>
         </is>
       </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L65" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -40090,9 +40438,9 @@
           <t>signorinimarco@helvetia.it</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L66" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -40166,9 +40514,9 @@
           <t>marco.nostini@nobisassicurazioni.it</t>
         </is>
       </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L67" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -40478,9 +40826,9 @@
           <t>riccardo.resciniti@fondoespero.it</t>
         </is>
       </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L71" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -40498,7 +40846,11 @@
           <t>[UNVERIFIED] — public-sector caution</t>
         </is>
       </c>
-      <c r="P71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -40576,7 +40928,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -40794,9 +41146,9 @@
           <t>matteo.colamussi@fondopriamo.it</t>
         </is>
       </c>
-      <c r="L75" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L75" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -40814,7 +41166,11 @@
           <t>[UNVERIFIED] — verify FIA stance</t>
         </is>
       </c>
-      <c r="P75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -40998,9 +41354,9 @@
           <t>sabina.valentini@filcoopsanitario.it</t>
         </is>
       </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L78" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -41074,9 +41430,9 @@
           <t>fabio.barigazzi@alifond.it</t>
         </is>
       </c>
-      <c r="L79" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L79" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -41094,7 +41450,11 @@
           <t>[UNVERIFIED] — verify</t>
         </is>
       </c>
-      <c r="P79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -41172,7 +41532,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -41230,9 +41590,9 @@
           <t>claudiovarani@fondotelemaco.it / c.varani70@gmail.com  (found on linked in)</t>
         </is>
       </c>
-      <c r="L81" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L81" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -41250,7 +41610,11 @@
           <t>[UNVERIFIED] — verify FIA stance</t>
         </is>
       </c>
-      <c r="P81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -41386,9 +41750,9 @@
           <t>fabio.cappuccio@previmoda.it</t>
         </is>
       </c>
-      <c r="L83" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L83" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -41406,7 +41770,11 @@
           <t>[UNVERIFIED] — verify Economia Reale membership</t>
         </is>
       </c>
-      <c r="P83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -41462,9 +41830,9 @@
           <t>andrea.laruccia@previbank.it</t>
         </is>
       </c>
-      <c r="L84" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L84" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -41482,7 +41850,11 @@
           <t>[UNVERIFIED] — verify</t>
         </is>
       </c>
-      <c r="P84" s="2" t="inlineStr"/>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -41538,9 +41910,9 @@
           <t>d.ballarin@prevedi.it</t>
         </is>
       </c>
-      <c r="L85" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L85" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -41558,7 +41930,11 @@
           <t>[UNVERIFIED] — verify FIA stance</t>
         </is>
       </c>
-      <c r="P85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -41614,9 +41990,9 @@
           <t>marco@prevaer.it</t>
         </is>
       </c>
-      <c r="L86" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L86" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -41634,7 +42010,11 @@
           <t>[UNVERIFIED] — verify membership</t>
         </is>
       </c>
-      <c r="P86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -41690,9 +42070,9 @@
           <t>riccardor@fondoperseosirio.it</t>
         </is>
       </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L87" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -41710,7 +42090,11 @@
           <t>[UNVERIFIED] — public-sector caution</t>
         </is>
       </c>
-      <c r="P87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -41846,9 +42230,9 @@
           <t>s.mirenghi@fondosanita.it</t>
         </is>
       </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L89" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -41866,7 +42250,11 @@
           <t>[UNVERIFIED] — verify</t>
         </is>
       </c>
-      <c r="P89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -41922,9 +42310,9 @@
           <t>spierini@fondoeurofer.it</t>
         </is>
       </c>
-      <c r="L90" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L90" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -41942,7 +42330,11 @@
           <t>[UNVERIFIED] — verify</t>
         </is>
       </c>
-      <c r="P90" s="2" t="inlineStr"/>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -41998,9 +42390,9 @@
           <t>fondoposte@fondoposte.it</t>
         </is>
       </c>
-      <c r="L91" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L91" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -42018,7 +42410,11 @@
           <t>[UNVERIFIED] — UNGATED — DG Metta + published fund address (fondoposte.it) — replaced wrong-desk import contact (Del Fante = Poste group CEO) — new president Antonio Nervi, board mandate to Bilancio 2025</t>
         </is>
       </c>
-      <c r="P91" s="2" t="inlineStr"/>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -42074,9 +42470,9 @@
           <t>massimiliano.spadari@fondogommaplastica.it</t>
         </is>
       </c>
-      <c r="L92" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L92" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -42094,7 +42490,11 @@
           <t>[UNVERIFIED] — verify Economia Reale membership</t>
         </is>
       </c>
-      <c r="P92" s="2" t="inlineStr"/>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -42150,9 +42550,9 @@
           <t>james.giovanardi@foncer.it</t>
         </is>
       </c>
-      <c r="L93" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L93" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -42170,7 +42570,11 @@
           <t>[UNVERIFIED] — verify membership</t>
         </is>
       </c>
-      <c r="P93" s="2" t="inlineStr"/>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -42226,9 +42630,9 @@
           <t>budassi@previdenzacooperativa.it</t>
         </is>
       </c>
-      <c r="L94" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L94" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -42246,7 +42650,11 @@
           <t>[UNVERIFIED] — verify</t>
         </is>
       </c>
-      <c r="P94" s="2" t="inlineStr"/>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -42302,9 +42710,9 @@
           <t>a.gentile@fondobyblos.it</t>
         </is>
       </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L95" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -42322,7 +42730,11 @@
           <t>[UNVERIFIED] — verify</t>
         </is>
       </c>
-      <c r="P95" s="2" t="inlineStr"/>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -42445,7 +42857,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Artur Trela</t>
+          <t>Andrzej Sołdek</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -42455,7 +42867,7 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>FIND: artur.trela@pzu.pl (group pattern)</t>
+          <t>Andrzej.Sołdek@pzu.pl</t>
         </is>
       </c>
       <c r="L97" s="8" t="inlineStr">
@@ -42475,7 +42887,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>[UNVERIFIED] — UNGATED — new right desk: Trela is ex-PZU Managing Director for Investments — 2026 group restructuring emphasises alternative and infrastructure investments (pzu.pl/bank.pl)</t>
+          <t>[CONFIRMED] — address confirmed 2026-08-03 by Michal from the actual send. Supersedes the unverified group-pattern guess artur.trela@pzu.pl.</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -42538,9 +42950,9 @@
           <t>jaroslaw.parkot@warta.pl</t>
         </is>
       </c>
-      <c r="L98" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L98" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -42558,7 +42970,11 @@
           <t>[UNVERIFIED] — CLUSTER→Talanx (no pipeline lead) — verify local discretion</t>
         </is>
       </c>
-      <c r="P98" s="2" t="inlineStr"/>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -42614,9 +43030,9 @@
           <t>tomasz.krzaczkowski@allianz.pl</t>
         </is>
       </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L99" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -42634,7 +43050,11 @@
           <t>[UNVERIFIED] — CLUSTER→allianz-pensionskasse-ag — AIM-framed</t>
         </is>
       </c>
-      <c r="P99" s="2" t="inlineStr"/>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -42690,9 +43110,9 @@
           <t>roger.hodgkiss@generali.pl</t>
         </is>
       </c>
-      <c r="L100" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L100" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -42766,9 +43186,9 @@
           <t>anna.wlodarczyk-moczkowska@compensa.pl</t>
         </is>
       </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L101" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -42842,9 +43262,9 @@
           <t>piotr.narloch@interrisk.pl</t>
         </is>
       </c>
-      <c r="L102" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L102" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -42970,9 +43390,9 @@
           <t>jaroslaw.matusiewicz@tuz.pl</t>
         </is>
       </c>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L104" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -43046,9 +43466,9 @@
           <t>sudzinska.grazyna@link4.pl</t>
         </is>
       </c>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L105" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
@@ -43122,9 +43542,9 @@
           <t>mariusz.kurowski@benefia.pl</t>
         </is>
       </c>
-      <c r="L106" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L106" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
@@ -43198,9 +43618,9 @@
           <t>artur.borowinski@ergohestia.pl</t>
         </is>
       </c>
-      <c r="L107" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L107" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
@@ -43218,7 +43638,11 @@
           <t>[UNVERIFIED] — CLUSTER→MEAG (no pipeline lead) — MEAG-managed — import name typo fixed (Borowiński)</t>
         </is>
       </c>
-      <c r="P107" s="2" t="inlineStr"/>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -43350,9 +43774,9 @@
           <t>bbanaskiewicz@polisa-zycie.pl</t>
         </is>
       </c>
-      <c r="L109" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L109" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
@@ -44146,9 +44570,9 @@
           <t>virgil.soncutean@allianztiriac.ro</t>
         </is>
       </c>
-      <c r="L120" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L120" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
@@ -44166,7 +44590,11 @@
           <t>[UNVERIFIED] — market leader — pairs with AZT row</t>
         </is>
       </c>
-      <c r="P120" s="2" t="inlineStr"/>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -44222,9 +44650,9 @@
           <t>calin.matei@groupama.ro</t>
         </is>
       </c>
-      <c r="L121" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L121" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
@@ -44242,7 +44670,11 @@
           <t>[UNVERIFIED] — Paris-framed</t>
         </is>
       </c>
-      <c r="P121" s="2" t="inlineStr"/>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -44298,9 +44730,9 @@
           <t>adrian.marin@generali.ro</t>
         </is>
       </c>
-      <c r="L122" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L122" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
@@ -44374,9 +44806,9 @@
           <t>madalin.rosu@asirom.ro</t>
         </is>
       </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L123" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
@@ -44450,9 +44882,9 @@
           <t>mihai.tecau@omniasig.ro</t>
         </is>
       </c>
-      <c r="L124" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L124" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
@@ -44526,9 +44958,9 @@
           <t>mesut.yetiskul@signal-iduna.ro</t>
         </is>
       </c>
-      <c r="L125" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L125" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
@@ -44678,9 +45110,9 @@
           <t>dragos-marius.calin@grawe.ro</t>
         </is>
       </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L127" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
@@ -44754,9 +45186,9 @@
           <t>kuldeep.kaushik@nn.ro</t>
         </is>
       </c>
-      <c r="L128" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L128" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
@@ -44774,7 +45206,11 @@
           <t>[UNVERIFIED] — life leader — import contact name had spelling variants</t>
         </is>
       </c>
-      <c r="P128" s="2" t="inlineStr"/>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -44830,9 +45266,9 @@
           <t>stavrositus@bcrasigviata.ro</t>
         </is>
       </c>
-      <c r="L129" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L129" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
@@ -44928,7 +45364,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -44986,9 +45422,9 @@
           <t>anita@eurolife-asigurari.ro</t>
         </is>
       </c>
-      <c r="L131" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L131" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
@@ -45308,7 +45744,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -45366,9 +45802,9 @@
           <t>raluca.morar@brd.ro</t>
         </is>
       </c>
-      <c r="L136" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L136" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
@@ -45386,7 +45822,11 @@
           <t>[UNVERIFIED] — verification-first</t>
         </is>
       </c>
-      <c r="P136" s="2" t="inlineStr"/>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -45522,9 +45962,9 @@
           <t>adrian.negru@raiffeisen.ro</t>
         </is>
       </c>
-      <c r="L138" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L138" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
@@ -45598,9 +46038,9 @@
           <t>anne-marie.mancas@generali.ro</t>
         </is>
       </c>
-      <c r="L139" s="9" t="inlineStr">
-        <is>
-          <t>drafted</t>
+      <c r="L139" s="8" t="inlineStr">
+        <is>
+          <t>sent</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
@@ -45618,7 +46058,11 @@
           <t>[UNVERIFIED] — fund name is Aripi — verify AUM</t>
         </is>
       </c>
-      <c r="P139" s="2" t="inlineStr"/>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -45674,9 +46118,9 @@
           <t>marius.ratiu@carpathiapensii.ro</t>
         </is>
       </c>
-      <c r="L140" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L140" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
@@ -45750,9 +46194,9 @@
           <t>corina@btpensii.ro</t>
         </is>
       </c>
-      <c r="L141" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L141" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
@@ -45826,9 +46270,9 @@
           <t>dan.sucu@confederatia-concordia.ro</t>
         </is>
       </c>
-      <c r="L142" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L142" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr"/>
@@ -45898,9 +46342,9 @@
           <t>blaz.hribar@pd-a.si</t>
         </is>
       </c>
-      <c r="L143" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L143" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
@@ -46182,9 +46626,9 @@
           <t>gregor.rovansek@prva.si</t>
         </is>
       </c>
-      <c r="L147" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L147" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
@@ -46338,9 +46782,9 @@
           <t>saso.smigic@generali-investments.si</t>
         </is>
       </c>
-      <c r="L149" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L149" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
@@ -46414,9 +46858,9 @@
           <t>andrej@sava-pokojninska.si</t>
         </is>
       </c>
-      <c r="L150" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L150" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
@@ -46490,9 +46934,9 @@
           <t>aljosha.urshic@triglav.si</t>
         </is>
       </c>
-      <c r="L151" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L151" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
@@ -46646,9 +47090,9 @@
           <t>vanja.horvat@generali.com</t>
         </is>
       </c>
-      <c r="L153" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L153" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
@@ -46722,9 +47166,9 @@
           <t>david.kastelic@grawe.si</t>
         </is>
       </c>
-      <c r="L154" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L154" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
@@ -46874,9 +47318,9 @@
           <t>natasa.hajdinjak@prva.si</t>
         </is>
       </c>
-      <c r="L156" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L156" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
@@ -47014,9 +47458,9 @@
           <t>barbara.smolnikar@zav-vita.si</t>
         </is>
       </c>
-      <c r="L158" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L158" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
@@ -47226,9 +47670,9 @@
           <t>dario.scannapieco@cdp.it</t>
         </is>
       </c>
-      <c r="L161" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L161" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
@@ -47302,9 +47746,9 @@
           <t>reinis.berzins@altum.lv</t>
         </is>
       </c>
-      <c r="L162" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L162" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
@@ -47454,9 +47898,9 @@
           <t>n.calvino@eib.org</t>
         </is>
       </c>
-      <c r="L164" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L164" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
@@ -47678,9 +48122,9 @@
           <t>manuel.munoz@ico.es</t>
         </is>
       </c>
-      <c r="L167" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L167" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
@@ -47898,9 +48342,9 @@
           <t>jost.dolnicar@zav-sava.si</t>
         </is>
       </c>
-      <c r="L170" s="2" t="inlineStr">
-        <is>
-          <t>research</t>
+      <c r="L170" s="9" t="inlineStr">
+        <is>
+          <t>drafted</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
